--- a/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/05_Segundo_Turno_Lula_vs_Caiado.xlsx
+++ b/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/05_Segundo_Turno_Lula_vs_Caiado.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,6 +762,17 @@
       </c>
       <c r="C29" t="n">
         <v>45.37832379484044</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B30" t="n">
+        <v>53.21924817907776</v>
+      </c>
+      <c r="C30" t="n">
+        <v>46.78075182092223</v>
       </c>
     </row>
   </sheetData>
@@ -775,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,6 +1112,17 @@
       </c>
       <c r="C29" t="n">
         <v>43.55624670793222</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B30" t="n">
+        <v>51.59383797207091</v>
+      </c>
+      <c r="C30" t="n">
+        <v>45.15534161391538</v>
       </c>
     </row>
   </sheetData>
@@ -1114,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1442,6 +1464,17 @@
         <v>47.20040088174866</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B30" t="n">
+        <v>54.84465838608461</v>
+      </c>
+      <c r="C30" t="n">
+        <v>48.40616202792908</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/05_Segundo_Turno_Lula_vs_Caiado.xlsx
+++ b/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/05_Segundo_Turno_Lula_vs_Caiado.xlsx
@@ -10,8 +10,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suavizados" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC_Baixo" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC_Alto" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodologia" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Suavizados'!$A$1:$C$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'IC_Baixo'!$A$1:$C$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IC_Alto'!$A$1:$C$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cobertura'!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Metodologia'!$A$1:$B$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -22,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,16 +41,25 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -56,11 +73,16 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -68,8 +90,17 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -436,346 +467,363 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Caiado</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Ronaldo Caiado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>46028</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="6" t="n">
         <v>55.40229885057472</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="6" t="n">
         <v>44.59770114942528</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>46035</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="6" t="n">
         <v>55.94437485153726</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="6" t="n">
         <v>44.05562514846274</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>46042</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="6" t="n">
         <v>56.11754763199608</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="6" t="n">
         <v>43.88245236800392</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>46049</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="6" t="n">
         <v>55.61432641336025</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="6" t="n">
         <v>44.38567358663975</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>46056</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="6" t="n">
         <v>56.03121586996147</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="6" t="n">
         <v>43.96878413003854</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>46063</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="6" t="n">
         <v>56.06635047962094</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="6" t="n">
         <v>43.93364952037906</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>46070</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="6" t="n">
         <v>55.78137904520533</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="6" t="n">
         <v>44.21862095479467</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>46077</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="6" t="n">
         <v>55.09267465689076</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="6" t="n">
         <v>44.90732534310925</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>46084</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="6" t="n">
         <v>55.33194731639198</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="6" t="n">
         <v>44.66805268360804</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>46091</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="6" t="n">
         <v>55.30112943945137</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="6" t="n">
         <v>44.69887056054864</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>46098</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="6" t="n">
         <v>55.10008247857708</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="6" t="n">
         <v>44.89991752142293</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>46105</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="6" t="n">
         <v>55.32381822221392</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="6" t="n">
         <v>44.67618177778608</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>46112</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="6" t="n">
         <v>55.50958407838976</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="6" t="n">
         <v>44.49041592161024</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>46119</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="6" t="n">
         <v>54.97333104071904</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="6" t="n">
         <v>45.02666895928097</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>46126</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="6" t="n">
         <v>54.24664033747721</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="6" t="n">
         <v>45.7533596625228</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>46133</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="6" t="n">
         <v>53.93645699681731</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="6" t="n">
         <v>46.0635430031827</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>46140</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="6" t="n">
         <v>53.48523664803194</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="6" t="n">
         <v>46.51476335196807</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>46147</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="6" t="n">
         <v>53.47055959615383</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="6" t="n">
         <v>46.52944040384617</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>46154</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="6" t="n">
         <v>53.98402910464777</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="6" t="n">
         <v>46.01597089535223</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>46160</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="6" t="n">
         <v>54.68602037881872</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="6" t="n">
         <v>45.31397962118126</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>46167</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="6" t="n">
         <v>55.16474032637745</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="6" t="n">
         <v>44.83525967362255</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>46174</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="6" t="n">
         <v>55.17945788428609</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="6" t="n">
         <v>44.82054211571392</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="6" t="n">
         <v>55.01300222592919</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="6" t="n">
         <v>44.9869977740708</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>46188</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="6" t="n">
         <v>54.92517926239721</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="6" t="n">
         <v>45.0748207376028</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>46195</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="6" t="n">
         <v>54.61704230707747</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="6" t="n">
         <v>45.38295769292254</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>46202</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="6" t="n">
         <v>54.5963112605267</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="6" t="n">
         <v>45.4036887394733</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>46209</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="6" t="n">
         <v>54.60524955160256</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="6" t="n">
         <v>45.39475044839743</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>46216</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="6" t="n">
         <v>54.62167620515956</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="6" t="n">
         <v>45.37832379484044</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>54.87126360210056</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>45.12873639789943</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
         <v>46224</v>
       </c>
-      <c r="B30" t="n">
-        <v>53.21924817907776</v>
-      </c>
-      <c r="C30" t="n">
-        <v>46.78075182092223</v>
+      <c r="B31" s="6" t="n">
+        <v>53.74731055131911</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>46.2526894486809</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -786,346 +834,363 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Caiado</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Ronaldo Caiado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>46028</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="6" t="n">
         <v>51.42495997513031</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="6" t="n">
         <v>40.62036227398087</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>46035</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="6" t="n">
         <v>53.13420086108722</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="6" t="n">
         <v>41.2454511580127</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>46042</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="6" t="n">
         <v>53.82062643744369</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="6" t="n">
         <v>41.58553117345154</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>46049</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="6" t="n">
         <v>53.61480814842517</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="6" t="n">
         <v>42.38615532170467</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>46056</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="6" t="n">
         <v>54.21540742563225</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="6" t="n">
         <v>42.15297568570932</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>46063</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="6" t="n">
         <v>54.25041133198251</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="6" t="n">
         <v>42.11771037274063</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>46070</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="6" t="n">
         <v>53.96410230509481</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="6" t="n">
         <v>42.40134421468416</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>46077</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="6" t="n">
         <v>53.27276789687677</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="6" t="n">
         <v>43.08741858309526</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>46084</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="6" t="n">
         <v>53.5126929115791</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="6" t="n">
         <v>42.84879827879517</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>46091</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="6" t="n">
         <v>53.48226463549977</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="6" t="n">
         <v>42.88000575659704</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>46098</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="6" t="n">
         <v>53.28044937674431</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="6" t="n">
         <v>43.08028441959016</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>46105</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="6" t="n">
         <v>53.50505009118505</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="6" t="n">
         <v>42.85741364675721</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>46112</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="6" t="n">
         <v>53.69076680250311</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="6" t="n">
         <v>42.67159864572359</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>46119</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="6" t="n">
         <v>53.15245604009766</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="6" t="n">
         <v>43.20579395865959</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>46126</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="6" t="n">
         <v>52.42350238341496</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="6" t="n">
         <v>43.93022170846055</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>46133</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="6" t="n">
         <v>52.11217610114</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="6" t="n">
         <v>44.23926210750539</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>46140</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="6" t="n">
         <v>51.65972858224392</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="6" t="n">
         <v>44.68925528618006</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>46147</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="6" t="n">
         <v>51.64534008284533</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="6" t="n">
         <v>44.70422089053767</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>46154</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="6" t="n">
         <v>52.16083240068116</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="6" t="n">
         <v>44.19277419138562</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>46160</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="6" t="n">
         <v>52.87470254932676</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="6" t="n">
         <v>43.50266179168929</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>46167</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="6" t="n">
         <v>53.3554755565991</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="6" t="n">
         <v>43.02599490384419</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>46174</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="6" t="n">
         <v>53.36966787442054</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="6" t="n">
         <v>43.01075210584838</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="6" t="n">
         <v>53.20118071483279</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="6" t="n">
         <v>43.1751762629744</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>46188</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="6" t="n">
         <v>53.10411600984452</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="6" t="n">
         <v>43.25375748505011</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>46195</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="6" t="n">
         <v>52.7949725289135</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="6" t="n">
         <v>43.56088791475857</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>46202</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="6" t="n">
         <v>52.7744549929143</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="6" t="n">
         <v>43.5818324718609</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>46209</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="6" t="n">
         <v>52.78326617243815</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="6" t="n">
         <v>43.57276706923301</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>46216</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="6" t="n">
         <v>52.79959911825134</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="6" t="n">
         <v>43.55624670793222</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>53.05048475104724</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>43.30795754684611</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
         <v>46224</v>
       </c>
-      <c r="B30" t="n">
-        <v>51.59383797207091</v>
-      </c>
-      <c r="C30" t="n">
-        <v>45.15534161391538</v>
+      <c r="B31" s="6" t="n">
+        <v>52.22257268827281</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>44.72795158563459</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1136,346 +1201,545 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Lula</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Caiado</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Ronaldo Caiado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>46028</v>
       </c>
+      <c r="B2" s="6" t="n">
+        <v>59.37963772601913</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>48.57504002486969</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>58.7545488419873</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>46.86579913891278</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>58.41446882654846</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>46.17937356255631</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>57.61384467829532</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>46.38519185157482</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>57.84702431429069</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>45.78459257436776</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>57.88228962725938</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>45.74958866801749</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>57.59865578531584</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>46.03589769490519</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>56.91258141690476</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>46.72723210312324</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>57.15120172120485</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>46.48730708842091</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>57.11999424340296</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>46.51773536450024</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>56.91971558040984</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>46.71955062325569</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>57.1425863532428</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>46.49494990881496</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>57.32840135427642</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>46.30923319749689</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>56.79420604134042</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>46.84754395990235</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>56.06977829153946</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>47.57649761658506</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>55.76073789249462</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>47.88782389886001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>55.31074471381995</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>48.34027141775609</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>55.29577910946234</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>48.35465991715468</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>55.80722580861438</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>47.83916759931884</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>56.49733820831069</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>47.12529745067323</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>56.97400509615581</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>46.6445244434009</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>56.98924789415163</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>46.63033212557946</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>56.8248237370256</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>46.79881928516721</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>56.7462425149499</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>46.89588399015549</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>56.43911208524143</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>47.2050274710865</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>56.41816752813911</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>47.22554500708571</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>56.42723293076698</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>47.21673382756185</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>56.44375329206778</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>47.20040088174866</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>56.69204245315387</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>46.94951524895275</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>55.27204841436541</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>47.7774273117272</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C31"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>indicador</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>observacoes_utilizadas</t>
+        </is>
+      </c>
       <c r="B2" t="n">
-        <v>59.37963772601913</v>
-      </c>
-      <c r="C2" t="n">
-        <v>48.57504002486969</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>46035</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>datas_distintas</t>
+        </is>
       </c>
       <c r="B3" t="n">
-        <v>58.7545488419873</v>
-      </c>
-      <c r="C3" t="n">
-        <v>46.86579913891278</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>46042</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>institutos_distintos</t>
+        </is>
       </c>
       <c r="B4" t="n">
-        <v>58.41446882654846</v>
-      </c>
-      <c r="C4" t="n">
-        <v>46.17937356255631</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>46049</v>
-      </c>
-      <c r="B5" t="n">
-        <v>57.61384467829532</v>
-      </c>
-      <c r="C5" t="n">
-        <v>46.38519185157482</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>primeira_data</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>46028</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>46056</v>
-      </c>
-      <c r="B6" t="n">
-        <v>57.84702431429069</v>
-      </c>
-      <c r="C6" t="n">
-        <v>45.78459257436776</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ultima_data</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>46224</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>46063</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>fallbacks_de_amostra</t>
+        </is>
       </c>
       <c r="B7" t="n">
-        <v>57.88228962725938</v>
-      </c>
-      <c r="C7" t="n">
-        <v>45.74958866801749</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>46070</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57.59865578531584</v>
-      </c>
-      <c r="C8" t="n">
-        <v>46.03589769490519</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>46077</v>
-      </c>
-      <c r="B9" t="n">
-        <v>56.91258141690476</v>
-      </c>
-      <c r="C9" t="n">
-        <v>46.72723210312324</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>46084</v>
-      </c>
-      <c r="B10" t="n">
-        <v>57.15120172120485</v>
-      </c>
-      <c r="C10" t="n">
-        <v>46.48730708842091</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>46091</v>
-      </c>
-      <c r="B11" t="n">
-        <v>57.11999424340296</v>
-      </c>
-      <c r="C11" t="n">
-        <v>46.51773536450024</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B12" t="n">
-        <v>56.91971558040984</v>
-      </c>
-      <c r="C12" t="n">
-        <v>46.71955062325569</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>46105</v>
-      </c>
-      <c r="B13" t="n">
-        <v>57.1425863532428</v>
-      </c>
-      <c r="C13" t="n">
-        <v>46.49494990881496</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B14" t="n">
-        <v>57.32840135427642</v>
-      </c>
-      <c r="C14" t="n">
-        <v>46.30923319749689</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>46119</v>
-      </c>
-      <c r="B15" t="n">
-        <v>56.79420604134042</v>
-      </c>
-      <c r="C15" t="n">
-        <v>46.84754395990235</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>46126</v>
-      </c>
-      <c r="B16" t="n">
-        <v>56.06977829153946</v>
-      </c>
-      <c r="C16" t="n">
-        <v>47.57649761658506</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B17" t="n">
-        <v>55.76073789249462</v>
-      </c>
-      <c r="C17" t="n">
-        <v>47.88782389886001</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>46140</v>
-      </c>
-      <c r="B18" t="n">
-        <v>55.31074471381995</v>
-      </c>
-      <c r="C18" t="n">
-        <v>48.34027141775609</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>46147</v>
-      </c>
-      <c r="B19" t="n">
-        <v>55.29577910946234</v>
-      </c>
-      <c r="C19" t="n">
-        <v>48.35465991715468</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>46154</v>
-      </c>
-      <c r="B20" t="n">
-        <v>55.80722580861438</v>
-      </c>
-      <c r="C20" t="n">
-        <v>47.83916759931884</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>46160</v>
-      </c>
-      <c r="B21" t="n">
-        <v>56.49733820831069</v>
-      </c>
-      <c r="C21" t="n">
-        <v>47.12529745067323</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>46167</v>
-      </c>
-      <c r="B22" t="n">
-        <v>56.97400509615581</v>
-      </c>
-      <c r="C22" t="n">
-        <v>46.6445244434009</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B23" t="n">
-        <v>56.98924789415163</v>
-      </c>
-      <c r="C23" t="n">
-        <v>46.63033212557946</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>46181</v>
-      </c>
-      <c r="B24" t="n">
-        <v>56.8248237370256</v>
-      </c>
-      <c r="C24" t="n">
-        <v>46.79881928516721</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>46188</v>
-      </c>
-      <c r="B25" t="n">
-        <v>56.7462425149499</v>
-      </c>
-      <c r="C25" t="n">
-        <v>46.89588399015549</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>46195</v>
-      </c>
-      <c r="B26" t="n">
-        <v>56.43911208524143</v>
-      </c>
-      <c r="C26" t="n">
-        <v>47.2050274710865</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>46202</v>
-      </c>
-      <c r="B27" t="n">
-        <v>56.41816752813911</v>
-      </c>
-      <c r="C27" t="n">
-        <v>47.22554500708571</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>46209</v>
-      </c>
-      <c r="B28" t="n">
-        <v>56.42723293076698</v>
-      </c>
-      <c r="C28" t="n">
-        <v>47.21673382756185</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>46216</v>
-      </c>
-      <c r="B29" t="n">
-        <v>56.44375329206778</v>
-      </c>
-      <c r="C29" t="n">
-        <v>47.20040088174866</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>46224</v>
-      </c>
-      <c r="B30" t="n">
-        <v>54.84465838608461</v>
-      </c>
-      <c r="C30" t="n">
-        <v>48.40616202792908</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>descricao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Base dos percentuais</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Votos válidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Denominador</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Reescala apenas Lula e o adversário para somarem 100%; brancos, nulos e indecisos saem do denominador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Média ponderada</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Baseline legado em janela de 30 dias: qualidade do instituto, recência linear e tamanho de amostra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Faixa</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Faixa amostral aproximada de 1,96 erros-padrão; não incorpora heterogeneidade, efeito de instituto ou desenho amostral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Interpretação</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Agregado de pesquisas para acompanhamento; não é previsão eleitoral nem probabilidade de vitória.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>